--- a/leads_generados.xlsx
+++ b/leads_generados.xlsx
@@ -3,11 +3,12 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4080" yWindow="600" windowWidth="30240" windowHeight="17760" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4080" yWindow="600" windowWidth="30240" windowHeight="17760" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Pizzerías" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Peluquerías Sitges" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Enlaces demos" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,7 +27,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,15 +68,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -418,12 +446,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18.6640625" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="45.5" customWidth="1" min="6" max="6"/>
-    <col width="30.83203125" customWidth="1" min="7" max="7"/>
+    <col width="16.1640625" customWidth="1" min="7" max="7"/>
+    <col width="43.6640625" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,7 +483,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>URL Web (Netlify)</t>
+          <t>URL Web (GitHub)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -474,49 +503,49 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Pizzerías en Gavà</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Restaurante Pizzeria Isabella</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>631 43 14 48</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Carrer de Sant Lluís, 41, 08850 Gavà, Barcelona, España</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Gavà</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>https://restaurante-pizzeria-isabella-65120.netlify.app</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/restaurante-pizzeria-isabella-6</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/34631431448?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Restaurante%20Pizzeria%20Isabella</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>webs/restaurante-pizzeria-isabella-2/index.html</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>2026-05-25 17:35</t>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>webs/restaurante-pizzeria-isabella-6/index.html</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
         </is>
       </c>
     </row>
@@ -546,9 +575,9 @@
           <t>Gavà</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>https://casa-escarr-gav.netlify.app</t>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/casa-escarr-gav</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
@@ -563,7 +592,7 @@
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>2026-05-25 17:35</t>
+          <t>2026-05-25 19:34</t>
         </is>
       </c>
     </row>
@@ -593,9 +622,9 @@
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>https://da-dina-restaurante-y-pizzeria.netlify.app</t>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/da-dina-restaurante-y-pizzeria</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
@@ -610,1139 +639,1168 @@
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>2026-05-25 17:36</t>
+          <t>2026-05-25 19:34</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Pizzerías en Barcelona</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Pizzeria Romana</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>931 44 83 33</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Carrer de Roger, 10, Sants-Montjuïc, 08028 Barcelona, España</t>
         </is>
       </c>
-      <c r="E5" s="1" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>https://pizzeria-romana.netlify.app</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/pizzeria-romana-2</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/34931448333?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Pizzeria%20Romana</t>
         </is>
       </c>
-      <c r="H5" s="1" t="inlineStr">
-        <is>
-          <t>webs/pizzeria-romana/index.html</t>
-        </is>
-      </c>
-      <c r="I5" s="1" t="inlineStr">
-        <is>
-          <t>2026-05-25 17:38</t>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>webs/pizzeria-romana-2/index.html</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Pizzerías en Eixample Barcelona</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Restaurante Pizzeria Edén</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>642 85 70 96</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Carrer de Provença, 332, Eixample, 08037 Barcelona, España</t>
         </is>
       </c>
-      <c r="E6" s="1" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>https://restaurante-pizzeria-edn.netlify.app</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/restaurante-pizzeria-ed-n-2</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/34642857096?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Restaurante%20Pizzeria%20Ed%C3%A9n</t>
         </is>
       </c>
-      <c r="H6" s="1" t="inlineStr">
-        <is>
-          <t>webs/restaurante-pizzeria-edén/index.html</t>
-        </is>
-      </c>
-      <c r="I6" s="1" t="inlineStr">
-        <is>
-          <t>2026-05-25 17:39</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>webs/restaurante-pizzeria-edén-2/index.html</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Pizzerías en Eixample Barcelona</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>La Piazzetta GranVia</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>930 07 96 08</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Gran Via de les Corts Catalanes, 566, Eixample, 08011 Barcelona, España</t>
         </is>
       </c>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>https://la-piazzetta-granvia.netlify.app</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/la-piazzetta-granvia-2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/34930079608?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20La%20Piazzetta%20GranVia</t>
         </is>
       </c>
-      <c r="H7" s="1" t="inlineStr">
-        <is>
-          <t>webs/la-piazzetta-granvia/index.html</t>
-        </is>
-      </c>
-      <c r="I7" s="1" t="inlineStr">
-        <is>
-          <t>2026-05-25 17:39</t>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>webs/la-piazzetta-granvia-2/index.html</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Pizzerías en Gràcia Barcelona</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Peppe e Pizza Gracia | Pizzeria Barcelona</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>933 14 99 28</t>
         </is>
       </c>
-      <c r="D8" s="1" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Carrer de Torrijos, 53, Gràcia, 08012 Barcelona, España</t>
         </is>
       </c>
-      <c r="E8" s="1" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>https://peppe-e-pizza-gracia-pizzeria-barcelona.netlify.app</t>
-        </is>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/peppe-e-pizza-gracia-pizzeria-barcelona-2</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/34933149928?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Peppe%20e%20Pizza%20Gracia%20%7C%20Pizzeria%20Barcelona</t>
         </is>
       </c>
-      <c r="H8" s="1" t="inlineStr">
-        <is>
-          <t>webs/peppe-e-pizza-gracia-pizzeria-barcelona/index.html</t>
-        </is>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
-        <is>
-          <t>2026-05-25 17:42</t>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>webs/peppe-e-pizza-gracia-pizzeria-barcelona-2/index.html</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Pizzerías en Castelldefels</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>All'ombra del Castello</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>931 81 47 87</t>
         </is>
       </c>
-      <c r="D9" s="1" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Carrer del Pintor Serra Santa, 10, 08860 Castelldefels, Barcelona, España</t>
         </is>
       </c>
-      <c r="E9" s="1" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Castelldefels</t>
         </is>
       </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>https://allombra-del-castello.netlify.app</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/allombra-del-castello-2</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/34931814787?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20All%27ombra%20del%20Castello</t>
         </is>
       </c>
-      <c r="H9" s="1" t="inlineStr">
-        <is>
-          <t>webs/allombra-del-castello/index.html</t>
-        </is>
-      </c>
-      <c r="I9" s="1" t="inlineStr">
-        <is>
-          <t>2026-05-25 17:42</t>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>webs/allombra-del-castello-2/index.html</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Pizzerías en Castelldefels</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Restaurante Verde Luna</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>936 36 37 23</t>
         </is>
       </c>
-      <c r="D10" s="1" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Carrer de la Llibertat, 33, 08860 Castelldefels, Barcelona, España</t>
         </is>
       </c>
-      <c r="E10" s="1" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Castelldefels</t>
         </is>
       </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>https://restaurante-verde-luna.netlify.app</t>
-        </is>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/restaurante-verde-luna-2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/34936363723?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Restaurante%20Verde%20Luna</t>
         </is>
       </c>
-      <c r="H10" s="1" t="inlineStr">
-        <is>
-          <t>webs/restaurante-verde-luna/index.html</t>
-        </is>
-      </c>
-      <c r="I10" s="1" t="inlineStr">
-        <is>
-          <t>2026-05-25 17:43</t>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>webs/restaurante-verde-luna-2/index.html</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Pizzerías en L'Hospitalet de Llobregat</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Pizzeria Italiana Pappa e Pizza Cocina Italiana</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>933 82 52 45</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Carrer de la Unió, 35, 08902 L'Hospitalet de Llobregat, Barcelona, España</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>L'Hospitalet de Llobregat</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>https://pizzeria-italiana-pappa-e-pizza-cocina-italiana.netlify.app</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/pizzeria-italiana-pappa-e-pizza-cocina-italiana</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/34933825245?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Pizzeria%20Italiana%20Pappa%20e%20Pizza%20Cocina%20Italiana</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/redeploy-10/index.html</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-05-21 14:33</t>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>webs/pizzeria-italiana-pappa-e-pizza-cocina-italiana/index.html</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Pizzerías en Gavà</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Restaurante Pizzeria Isabella</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>631 43 14 48</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Carrer de Sant Lluís, 41, 08850 Gavà, Barcelona, España</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Gavà</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>https://restaurante-pizzeria-isabella-65522.netlify.app</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/restaurante-pizzeria-isabella-3</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/34631431448?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Restaurante%20Pizzeria%20Isabella</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/redeploy-11/index.html</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-05-21 14:33</t>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>webs/restaurante-pizzeria-isabella-3/index.html</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Pizzerías en Cornellà de Llobregat</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>El cuisto</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>931 26 53 85</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Carrer de Cornellà Modern, 62, 08940 Cornellà de Llobregat, Barcelona, España</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Cornellà de Llobregat</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>https://el-cuisto.netlify.app</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/el-cuisto</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/34931265385?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20El%20cuisto</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/redeploy-12/index.html</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-05-21 14:33</t>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>webs/el-cuisto/index.html</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Pizzerías en Barcelona</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>La Pizza Loca</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>933 31 30 44</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Carrer Creu Coberta, 64, Sants-Montjuïc, 08014 Barcelona, España</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>https://la-pizza-loca.netlify.app</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/la-pizza-loca-2</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/34933313044?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20La%20Pizza%20Loca</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/lead-new-1/index.html</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-05-21 15:46</t>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>webs/la-pizza-loca-2/index.html</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Pizzerías en Gràcia Barcelona</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Pizzería La Svolta</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>651 05 99 37</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Carrer de Pérez Galdós, 30, Gràcia, 08012 Barcelona, España</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>https://pizzera-la-svolta.netlify.app</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/pizzer-a-la-svolta-2</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/34651059937?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Pizzer%C3%ADa%20La%20Svolta</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/lead-new-2/index.html</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-05-21 15:47</t>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>webs/pizzería-la-svolta-2/index.html</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Pizzerías en Gràcia Barcelona</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Gracia Döner Kebab</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>936 43 41 82</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Carrer de Ramón y Cajal, 114, Gràcia, 08024 Barcelona, España</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>https://gracia-dner-kebab.netlify.app</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/gracia-d-ner-kebab</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/34936434182?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Gracia%20D%C3%B6ner%20Kebab</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/lead-new-3/index.html</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-05-21 15:48</t>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>webs/gracia-döner-kebab/index.html</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Pizzerías en Sants Barcelona</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Restaurante Putxinel·lis</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>936 11 24 85</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Carrer de Salou, 23, Sants-Montjuïc, 08014 Barcelona, España</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>https://restaurante-putxinellis.netlify.app</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/restaurante-putxinellis-2</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/34936112485?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Restaurante%20Putxinel%C2%B7lis</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/lead-new-4/index.html</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-05-21 15:48</t>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>webs/restaurante-putxinellis-2/index.html</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Pizzerías en Sants Barcelona</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Pizzería Artesanal Divina Stefy</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>932 89 03 02</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Gran Via de les Corts Catalanes, 351, Sants-Montjuïc, 08014 Barcelona, España</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>https://pizzera-artesanal-divina-stefy.netlify.app</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/pizzer-a-artesanal-divina-stefy-2</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/34932890302?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Pizzer%C3%ADa%20Artesanal%20Divina%20Stefy</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/lead-new-5/index.html</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-05-21 15:49</t>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>webs/pizzería-artesanal-divina-stefy-2/index.html</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Pizzerías en Sants Barcelona</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>El Cullerot de Sants</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>934 31 90 69</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Carrer d'Olzinelles, 114, Sants-Montjuïc, 08014 Barcelona, España</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>https://el-cullerot-de-sants.netlify.app</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/el-cullerot-de-sants-2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/34934319069?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20El%20Cullerot%20de%20Sants</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/lead-new-6/index.html</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-05-21 15:49</t>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>webs/el-cullerot-de-sants-2/index.html</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Pizzerías en Poblenou Barcelona</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Panepizza</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>936 43 80 56</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Carrer de Bilbao, 70, Sant Martí, 08005 Sant Martí de Maçana, Barcelona, España</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Sant Martí de Maçana</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>https://panepizza-71432.netlify.app</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/panepizza-2</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/34936438056?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Panepizza</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/lead-new-7/index.html</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-05-21 15:50</t>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>webs/panepizza-2/index.html</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Pizzerías en Poblenou Barcelona</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Brume Brunch| Poblenou Barcelona</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>930 16 51 39</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Av. d'Icària, 178, Sant Martí, 08005 Barcelona, España</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>https://brume-brunch-poblenou-barcelona.netlify.app</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/brume-brunch-poblenou-barcelona-2</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/34930165139?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Brume%20Brunch%7C%20Poblenou%20Barcelona</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/lead-new-8/index.html</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-05-21 15:51</t>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>webs/brume-brunch-poblenou-barcelona-2/index.html</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Pizzerías en Badalona</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Pizzeria Etna</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>933 88 77 90</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Carrer d'Alfons XII, 291, Local 2, 08912 Badalona, Barcelona, España</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Badalona</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>https://pizzeria-etna.netlify.app</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/pizzeria-etna-2</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/34933887790?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Pizzeria%20Etna</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/lead-new-9/index.html</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-05-21 15:51</t>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>webs/pizzeria-etna-2/index.html</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Pizzerías en Badalona</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Pizzeria San Marino</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>933 99 32 60</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Passeig Marítim, 5, 08912 Badalona, Barcelona, España</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Badalona</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>https://pizzeria-san-marino.netlify.app</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/pizzeria-san-marino-2</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/34933993260?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Pizzeria%20San%20Marino</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/lead-new-10/index.html</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2026-05-21 15:52</t>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>webs/pizzeria-san-marino-2/index.html</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Pizzerías en Badalona</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Ovvio pizzería</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>622 92 08 48</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Av. del President Companys, 10, 08911 Badalona, Barcelona, España</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Badalona</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>https://ovvio-pizzera.netlify.app</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/ovvio-pizzer-a-2</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/34622920848?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Ovvio%20pizzer%C3%ADa</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/lead-new-11/index.html</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-05-21 15:52</t>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>webs/ovvio-pizzería-2/index.html</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Pizzerías en Badalona</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Pizzicato Go! Badalona</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>747 74 66 52</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Carrer de Ribas i Perdigó, 31, 08911 Badalona, Barcelona, España</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Badalona</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>https://pizzicato-go-badalona.netlify.app</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/pizzicato-go-badalona-2</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/34747746652?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Pizzicato%20Go%21%20Badalona</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/lead-new-12/index.html</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2026-05-21 15:53</t>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>webs/pizzicato-go-badalona-2/index.html</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Pizzerías en L'Hospitalet de Llobregat</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Pizzeria Naranjito</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>934 22 84 54</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Carrer del Doctor Martí Julià, 174, 08903 L'Hospitalet de Llobregat, Barcelona, España</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>L'Hospitalet de Llobregat</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>https://pizzeria-naranjito.netlify.app</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/pizzeria-naranjito-2</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/34934228454?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Pizzeria%20Naranjito</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/lead-new-13/index.html</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2026-05-21 15:54</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>webs/pizzeria-naranjito-2/index.html</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Pizzerías en L'Hospitalet de Llobregat</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>il Mago Restaurante Pizzeria Italiana</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>663 51 01 41</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Carrer de Jacint Verdaguer, 27-29, 08902 L'Hospitalet de Llobregat, Barcelona, España</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>L'Hospitalet de Llobregat</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>https://il-mago-restaurante-pizzeria-italiana.netlify.app</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/il-mago-restaurante-pizzeria-italiana-2</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/34663510141?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20il%20Mago%20Restaurante%20Pizzeria%20Italiana</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/lead-new-14/index.html</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2026-05-21 15:54</t>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>webs/il-mago-restaurante-pizzeria-italiana-2/index.html</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Pizzerías en L'Hospitalet de Llobregat</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Pizza Rico Hospitalet</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>934 49 47 65</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Plaça Sénia, 4, 08904 L'Hospitalet de Llobregat, Barcelona, España</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>L'Hospitalet de Llobregat</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>https://pizza-rico-hospitalet.netlify.app</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/pizza-rico-hospitalet-2</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>https://wa.me/34934494765?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Pizza%20Rico%20Hospitalet</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/lead-new-15/index.html</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2026-05-21 15:55</t>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>webs/pizza-rico-hospitalet-2/index.html</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" display="https://xaviergp2003-gif.github.io/restaurante-pizzeria-isabella-6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" display="https://xaviergp2003-gif.github.io/casa-escarr-gav" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" display="https://xaviergp2003-gif.github.io/da-dina-restaurante-y-pizzeria" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" display="https://xaviergp2003-gif.github.io/pizzeria-romana-2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" display="https://xaviergp2003-gif.github.io/restaurante-pizzeria-ed-n-2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" display="https://xaviergp2003-gif.github.io/la-piazzetta-granvia-2" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" display="https://xaviergp2003-gif.github.io/peppe-e-pizza-gracia-pizzeria-barcelona-2" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" display="https://xaviergp2003-gif.github.io/allombra-del-castello-2" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" display="https://xaviergp2003-gif.github.io/restaurante-verde-luna-2" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" display="https://xaviergp2003-gif.github.io/pizzeria-italiana-pappa-e-pizza-cocina-italiana" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" display="https://xaviergp2003-gif.github.io/restaurante-pizzeria-isabella-3" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" display="https://xaviergp2003-gif.github.io/el-cuisto" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" display="https://xaviergp2003-gif.github.io/la-pizza-loca-2" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" display="https://xaviergp2003-gif.github.io/pizzer-a-la-svolta-2" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" display="https://xaviergp2003-gif.github.io/gracia-d-ner-kebab" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" display="https://xaviergp2003-gif.github.io/restaurante-putxinellis-2" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" display="https://xaviergp2003-gif.github.io/pizzer-a-artesanal-divina-stefy-2" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" display="https://xaviergp2003-gif.github.io/el-cullerot-de-sants-2" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" display="https://xaviergp2003-gif.github.io/panepizza-2" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" display="https://xaviergp2003-gif.github.io/brume-brunch-poblenou-barcelona-2" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" display="https://xaviergp2003-gif.github.io/pizzeria-etna-2" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" display="https://xaviergp2003-gif.github.io/pizzeria-san-marino-2" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" display="https://xaviergp2003-gif.github.io/ovvio-pizzer-a-2" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" display="https://xaviergp2003-gif.github.io/pizzicato-go-badalona-2" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" display="https://xaviergp2003-gif.github.io/pizzeria-naranjito-2" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" display="https://xaviergp2003-gif.github.io/il-mago-restaurante-pizzeria-italiana-2" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" display="https://xaviergp2003-gif.github.io/pizza-rico-hospitalet-2" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1754,7 +1812,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="24.33203125" customWidth="1" min="1" max="1"/>
     <col width="45.5" customWidth="1" min="6" max="6"/>
@@ -1762,523 +1820,2045 @@
   </cols>
   <sheetData>
     <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Peluquerías en Sitges</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Prestige Peluqueros Sitges</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>938 94 22 24</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Carrer Major, 25, 08870 Sitges, Barcelona, España</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Sitges</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>URL Web (GitHub)</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/34938942224?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Prestige%20Peluqueros%20Sitges</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>webs/prestige-peluqueros-sitges-3/index.html</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 18:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Peluquerías en Sitges</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Prestige Peluqueros Sitges</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>938 94 22 24</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de la Indústria, 17, 08870 Sitges, Barcelona, España</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Sitges</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/prestige-peluqueros-sitges-4</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/34938942224?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Prestige%20Peluqueros%20Sitges</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>webs/prestige-peluqueros-sitges-4/index.html</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Peluquerías en Sitges</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Global Belleza Peluqueria Sitges</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>603 75 04 90</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Sant Josep, 27, 08870 Sitges, Barcelona, España</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Sitges</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/global-belleza-peluqueria-sitges-2</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/34603750490?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Global%20Belleza%20Peluqueria%20Sitges</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>webs/global-belleza-peluqueria-sitges-2/index.html</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Peluquerías en Sitges</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Hair Studio ARTE DE BELLEZA by Emil Hintz</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>931 38 77 54</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Sant Bonaventura, 3, 08870 Sitges, Barcelona, España</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Sitges</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/hair-studio-arte-de-belleza-by-emil-hintz-2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/34931387754?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Hair%20Studio%20ARTE%20DE%20BELLEZA%20by%20Emil%20Hintz</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>webs/hair-studio-arte-de-belleza-by-emil-hintz-2/index.html</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Salón de belleza Sitges</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Belleza de Lidiia</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>605 38 09 56</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Santiago Rusiñol, 35, 08870 Sitges, Barcelona, España</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Sitges</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/belleza-de-lidiia-2</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/34605380956?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Belleza%20de%20Lidiia</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>webs/belleza-de-lidiia-2/index.html</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Salón de belleza Sitges</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Nou i Clàssic</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>938 11 18 48</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Av. Camí dels Capellans, 19, 08870 Sitges, Barcelona, España</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Sitges</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/nou-i-cl-ssic-2</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/34938111848?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Nou%20i%20Cl%C3%A0ssic</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>webs/nou-i-clàssic-2/index.html</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Peluquería unisex Sitges</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Peluqueria B&amp;M Unisex</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>931 89 68 39</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de la Maladeta, 15, 08906 Esplugues de Llobregat, Barcelona, España</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Esplugues de Llobregat</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/peluqueria-bm-unisex-2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/34931896839?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Peluqueria%20B%26M%20Unisex</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>webs/peluqueria-bm-unisex-2/index.html</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Peluquería unisex Sitges</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Peluqueria Cris Sitges S.L.</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>938 94 09 04</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Santiago Rusiñol, 31, 08870 Sitges, Barcelona, España</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Sitges</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/peluqueria-cris-sitges-sl-2</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/34938940904?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Peluqueria%20Cris%20Sitges%20S.L.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>webs/peluqueria-cris-sitges-sl-2/index.html</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Peluquería unisex Sitges</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Barberia Latín Art / Peluqueria Unisex Barber Shop</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>653 14 92 10</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Rambla del Brasil, 23, Sants-Montjuïc, 08028 Barcelona, España</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/barberia-lat-n-art-peluqueria-unisex-barber-shop-2</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/34653149210?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Barberia%20Lat%C3%ADn%20Art%20%2F%20Peluqueria%20Unisex%20Barber%20Shop</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>webs/barberia-latín-art-peluqueria-unisex-barber-shop-2/index.html</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Peluquería unisex Sitges</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>CAPS P</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>938 94 75 57</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Sant Josep, 17, 08870 Sitges, Barcelona, España</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Sitges</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/caps-p-2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/34938947557?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20CAPS%20P</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>webs/caps-p-2/index.html</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Barbería Sitges</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Arte &amp; Corte</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>931 89 78 06</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Carrer d'Espalter, 31, 08870 Sitges, Barcelona, España</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Sitges</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/arte-corte-2</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/34931897806?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Arte%20%26%20Corte</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>webs/arte-corte-2/index.html</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:34</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" display="https://xaviergp2003-gif.github.io/prestige-peluqueros-sitges-4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" display="https://xaviergp2003-gif.github.io/global-belleza-peluqueria-sitges-2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" display="https://xaviergp2003-gif.github.io/hair-studio-arte-de-belleza-by-emil-hintz-2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" display="https://xaviergp2003-gif.github.io/belleza-de-lidiia-2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" display="https://xaviergp2003-gif.github.io/nou-i-cl-ssic-2" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" display="https://xaviergp2003-gif.github.io/peluqueria-bm-unisex-2" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" display="https://xaviergp2003-gif.github.io/peluqueria-cris-sitges-sl-2" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" display="https://xaviergp2003-gif.github.io/barberia-lat-n-art-peluqueria-unisex-barber-shop-2" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" display="https://xaviergp2003-gif.github.io/caps-p-2" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" display="https://xaviergp2003-gif.github.io/arte-corte-2" r:id="rId11"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C83"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Peluquerías en Sitges</t>
+          <t>Carpeta webs</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Prestige Peluqueros Sitges</t>
+          <t>URL GitHub Pages</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>938 94 22 24</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Carrer Major, 25, 08870 Sitges, Barcelona, España</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Sitges</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>https://peluqueria-prestige-peluqueros-sitges.netlify.app</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>https://wa.me/34938942224?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Prestige%20Peluqueros%20Sitges</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/pelu-sitges-1/index.html</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>2026-05-21 17:50</t>
+          <t>Empresa (texto)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Peluquerías en Sitges</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Prestige Peluqueros Sitges</t>
+          <t>allombra-del-castello</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/allombra-del-castello</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>938 94 22 24</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Carrer de la Indústria, 17, 08870 Sitges, Barcelona, España</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Sitges</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://peluqueria-prestige-peluqueros-sitges.netlify.app</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://wa.me/34938942224?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Prestige%20Peluqueros%20Sitges</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/pelu-sitges-1/index.html</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-05-21 17:55</t>
+          <t>Allombra Del Castello</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Peluquerías en Sitges</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Global Belleza Peluqueria Sitges</t>
+          <t>allombra-del-castello-2</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/allombra-del-castello-2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>603 75 04 90</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Carrer de Sant Josep, 27, 08870 Sitges, Barcelona, España</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Sitges</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://peluqueria-global-belleza-peluqueria-sitges.netlify.app</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://wa.me/34603750490?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Global%20Belleza%20Peluqueria%20Sitges</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/pelu-sitges-2/index.html</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2026-05-21 17:50</t>
+          <t>Allombra Del Castello 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Peluquerías en Sitges</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Hair Studio ARTE DE BELLEZA by Emil Hintz</t>
+          <t>allombra-del-castello-3</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/allombra-del-castello-3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>931 38 77 54</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Carrer de Sant Bonaventura, 3, 08870 Sitges, Barcelona, España</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Sitges</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://peluqueria-hair-studio-arte-de-belleza-by-emil-hin.netlify.app</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://wa.me/34931387754?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Hair%20Studio%20ARTE%20DE%20BELLEZA%20by%20Emil%20Hintz</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/pelu-sitges-3/index.html</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2026-05-21 17:51</t>
+          <t>Allombra Del Castello 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Salón de belleza Sitges</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Belleza de Lidiia</t>
+          <t>arte-corte</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/arte-corte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>605 38 09 56</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Carrer de Santiago Rusiñol, 35, 08870 Sitges, Barcelona, España</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Sitges</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>https://peluqueria-belleza-de-lidiia.netlify.app</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://wa.me/34605380956?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Belleza%20de%20Lidiia</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/pelu-sitges-4/index.html</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-05-21 17:51</t>
+          <t>Arte Corte</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Salón de belleza Sitges</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Nou i Clàssic</t>
+          <t>arte-corte-2</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/arte-corte-2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>938 11 18 48</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Av. Camí dels Capellans, 19, 08870 Sitges, Barcelona, España</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Sitges</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>https://peluqueria-nou-i-clssic.netlify.app</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://wa.me/34938111848?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Nou%20i%20Cl%C3%A0ssic</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/pelu-sitges-5/index.html</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-05-21 17:52</t>
+          <t>Arte Corte 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Peluquería unisex Sitges</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Peluqueria B&amp;M Unisex</t>
+          <t>barberia-latín-art-peluqueria-unisex-barber-shop</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/barberia-lat-n-art-peluqueria-unisex-barber-shop</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>931 89 68 39</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Carrer de la Maladeta, 15, 08906 Esplugues de Llobregat, Barcelona, España</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Esplugues de Llobregat</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>https://peluqueria-peluqueria-bm-unisex.netlify.app</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://wa.me/34931896839?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Peluqueria%20B%26M%20Unisex</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/pelu-sitges-6/index.html</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-05-21 17:53</t>
+          <t>Barberia Latín Art Peluqueria Unisex Barber Shop</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Peluquería unisex Sitges</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Peluqueria Cris Sitges S.L.</t>
+          <t>barberia-latín-art-peluqueria-unisex-barber-shop-2</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/barberia-lat-n-art-peluqueria-unisex-barber-shop-2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>938 94 09 04</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Carrer de Santiago Rusiñol, 31, 08870 Sitges, Barcelona, España</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Sitges</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>https://peluqueria-peluqueria-cris-sitges-sl.netlify.app</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://wa.me/34938940904?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Peluqueria%20Cris%20Sitges%20S.L.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/pelu-sitges-7/index.html</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-05-21 17:53</t>
+          <t>Barberia Latín Art Peluqueria Unisex Barber Shop 2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Peluquería unisex Sitges</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Barberia Latín Art / Peluqueria Unisex Barber Shop</t>
+          <t>belleza-de-lidiia</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/belleza-de-lidiia</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>653 14 92 10</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Rambla del Brasil, 23, Sants-Montjuïc, 08028 Barcelona, España</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>https://peluqueria-barberia-latn-art-peluqueria-unisex-ba.netlify.app</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://wa.me/34653149210?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Barberia%20Lat%C3%ADn%20Art%20%2F%20Peluqueria%20Unisex%20Barber%20Shop</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/pelu-sitges-8/index.html</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-05-21 17:54</t>
+          <t>Belleza De Lidiia</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Peluquería unisex Sitges</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CAPS P</t>
+          <t>belleza-de-lidiia-2</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/belleza-de-lidiia-2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>938 94 75 57</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Carrer de Sant Josep, 17, 08870 Sitges, Barcelona, España</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Sitges</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>https://peluqueria-caps-p.netlify.app</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://wa.me/34938947557?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20CAPS%20P</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/pelu-sitges-9/index.html</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-05-21 17:54</t>
+          <t>Belleza De Lidiia 2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Barbería Sitges</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Arte &amp; Corte</t>
+          <t>brume-brunch-poblenou-barcelona</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/brume-brunch-poblenou-barcelona</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>931 89 78 06</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Carrer d'Espalter, 31, 08870 Sitges, Barcelona, España</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Sitges</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>https://peluqueria-arte-corte.netlify.app</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://wa.me/34931897806?text=Hola%2C%20he%20visto%20vuestra%20p%C3%A1gina%20web%20y%20me%20gustar%C3%ADa%20m%C3%A1s%20informaci%C3%B3n%20sobre%20Arte%20%26%20Corte</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>/Users/xagri/Documents/GitHub/Automatizacion pizzerias/dist/pelu-sitges-10/index.html</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-05-21 17:55</t>
+          <t>Brume Brunch Poblenou Barcelona</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>brume-brunch-poblenou-barcelona-2</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/brume-brunch-poblenou-barcelona-2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Brume Brunch Poblenou Barcelona 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>caps-p</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/caps-p</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Caps P</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>caps-p-2</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/caps-p-2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Caps P 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>casa-escarré-gavá</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/casa-escarr-gav</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Casa Escarré Gavá</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>casa-escarré-gavá-2</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/casa-escarr-gav-2</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Casa Escarré Gavá 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>da-dina-restaurante-y-pizzeria</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/da-dina-restaurante-y-pizzeria</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Da Dina Restaurante Y Pizzeria</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>el-cuisto</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/el-cuisto</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>El Cuisto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>el-cuisto-2</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/el-cuisto-2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>El Cuisto 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>el-cullerot-de-sants</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/el-cullerot-de-sants</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>El Cullerot De Sants</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>el-cullerot-de-sants-2</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/el-cullerot-de-sants-2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>El Cullerot De Sants 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>global-belleza-peluqueria-sitges</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/global-belleza-peluqueria-sitges</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Global Belleza Peluqueria Sitges</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>global-belleza-peluqueria-sitges-2</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/global-belleza-peluqueria-sitges-2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Global Belleza Peluqueria Sitges 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>gracia-döner-kebab</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/gracia-d-ner-kebab</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Gracia Döner Kebab</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>gracia-döner-kebab-2</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/gracia-d-ner-kebab-2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Gracia Döner Kebab 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>hair-studio-arte-de-belleza-by-emil-hintz</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/hair-studio-arte-de-belleza-by-emil-hintz</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Hair Studio Arte De Belleza By Emil Hintz</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>hair-studio-arte-de-belleza-by-emil-hintz-2</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/hair-studio-arte-de-belleza-by-emil-hintz-2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Hair Studio Arte De Belleza By Emil Hintz 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>il-mago-restaurante-pizzeria-italiana</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/il-mago-restaurante-pizzeria-italiana</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Il Mago Restaurante Pizzeria Italiana</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>il-mago-restaurante-pizzeria-italiana-2</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/il-mago-restaurante-pizzeria-italiana-2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Il Mago Restaurante Pizzeria Italiana 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>il-nuovo-italiano-3</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/il-nuovo-italiano-3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Il Nuovo Italiano 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>la-piazzetta-granvia</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/la-piazzetta-granvia</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>La Piazzetta Granvia</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>la-piazzetta-granvia-2</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/la-piazzetta-granvia-2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>La Piazzetta Granvia 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>la-pizza-loca</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/la-pizza-loca</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>La Pizza Loca</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>la-pizza-loca-2</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/la-pizza-loca-2</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>La Pizza Loca 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>nou-i-clàssic</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/nou-i-cl-ssic</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Nou I Clàssic</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>nou-i-clàssic-2</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/nou-i-cl-ssic-2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Nou I Clàssic 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ovvio-pizzería</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/ovvio-pizzer-a</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovvio Pizzería</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ovvio-pizzería-2</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/ovvio-pizzer-a-2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovvio Pizzería 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>panepizza</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/panepizza</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Panepizza</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>panepizza-2</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/panepizza-2</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Panepizza 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>peluqueria-bm-unisex</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/peluqueria-bm-unisex</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Peluqueria Bm Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>peluqueria-bm-unisex-2</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/peluqueria-bm-unisex-2</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Peluqueria Bm Unisex 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>peluqueria-cris-sitges-sl</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/peluqueria-cris-sitges-sl</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Peluqueria Cris Sitges Sl</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>peluqueria-cris-sitges-sl-2</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/peluqueria-cris-sitges-sl-2</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Peluqueria Cris Sitges Sl 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>peppe-e-pizza-gracia-pizzeria-barcelona</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/peppe-e-pizza-gracia-pizzeria-barcelona</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Peppe E Pizza Gracia Pizzeria Barcelona</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>peppe-e-pizza-gracia-pizzeria-barcelona-2</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/peppe-e-pizza-gracia-pizzeria-barcelona-2</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Peppe E Pizza Gracia Pizzeria Barcelona 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>peppe-e-pizza-gracia-pizzeria-barcelona-3</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/peppe-e-pizza-gracia-pizzeria-barcelona-3</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Peppe E Pizza Gracia Pizzeria Barcelona 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>pizza-rico-hospitalet</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/pizza-rico-hospitalet</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Pizza Rico Hospitalet</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>pizza-rico-hospitalet-2</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/pizza-rico-hospitalet-2</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Pizza Rico Hospitalet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>pizzeria-etna</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/pizzeria-etna</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Pizzeria Etna</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>pizzeria-etna-2</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/pizzeria-etna-2</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Pizzeria Etna 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>pizzeria-italiana-pappa-e-pizza-cocina-italiana</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/pizzeria-italiana-pappa-e-pizza-cocina-italiana</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Pizzeria Italiana Pappa E Pizza Cocina Italiana</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>pizzeria-italiana-pappa-e-pizza-cocina-italiana-2</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/pizzeria-italiana-pappa-e-pizza-cocina-italiana-2</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Pizzeria Italiana Pappa E Pizza Cocina Italiana 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>pizzeria-naranjito</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/pizzeria-naranjito</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Pizzeria Naranjito</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>pizzeria-naranjito-2</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/pizzeria-naranjito-2</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Pizzeria Naranjito 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>pizzeria-romana</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/pizzeria-romana</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Pizzeria Romana</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>pizzeria-romana-2</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/pizzeria-romana-2</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Pizzeria Romana 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>pizzeria-san-marino</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/pizzeria-san-marino</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Pizzeria San Marino</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>pizzeria-san-marino-2</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/pizzeria-san-marino-2</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Pizzeria San Marino 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>pizzería-artesanal-divina-stefy</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/pizzer-a-artesanal-divina-stefy</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Pizzería Artesanal Divina Stefy</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>pizzería-artesanal-divina-stefy-2</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/pizzer-a-artesanal-divina-stefy-2</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Pizzería Artesanal Divina Stefy 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>pizzería-la-svolta</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/pizzer-a-la-svolta</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Pizzería La Svolta</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>pizzería-la-svolta-2</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/pizzer-a-la-svolta-2</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Pizzería La Svolta 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>pizzicato-go-badalona</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/pizzicato-go-badalona</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Pizzicato Go Badalona</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>pizzicato-go-badalona-2</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/pizzicato-go-badalona-2</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Pizzicato Go Badalona 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>prestige-peluqueros-sitges</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/prestige-peluqueros-sitges</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Prestige Peluqueros Sitges</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>prestige-peluqueros-sitges-2</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/prestige-peluqueros-sitges-2</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Prestige Peluqueros Sitges 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>prestige-peluqueros-sitges-3</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/prestige-peluqueros-sitges-3</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Prestige Peluqueros Sitges 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>prestige-peluqueros-sitges-4</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/prestige-peluqueros-sitges-4</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Prestige Peluqueros Sitges 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>restaurante-pizzeria-edén</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/restaurante-pizzeria-ed-n</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Restaurante Pizzeria Edén</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>restaurante-pizzeria-edén-2</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/restaurante-pizzeria-ed-n-2</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Restaurante Pizzeria Edén 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>restaurante-pizzeria-isabella</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/restaurante-pizzeria-isabella</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Restaurante Pizzeria Isabella</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>restaurante-pizzeria-isabella-1</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/restaurante-pizzeria-isabella-1</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Restaurante Pizzeria Isabella 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>restaurante-pizzeria-isabella-2</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/restaurante-pizzeria-isabella-2</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Restaurante Pizzeria Isabella 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>restaurante-pizzeria-isabella-3</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/restaurante-pizzeria-isabella-3</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Restaurante Pizzeria Isabella 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>restaurante-pizzeria-isabella-4</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/restaurante-pizzeria-isabella-4</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Restaurante Pizzeria Isabella 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>restaurante-pizzeria-isabella-5</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/restaurante-pizzeria-isabella-5</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Restaurante Pizzeria Isabella 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>restaurante-pizzeria-isabella-6</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/restaurante-pizzeria-isabella-6</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Restaurante Pizzeria Isabella 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>restaurante-putxinellis</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/restaurante-putxinellis</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Restaurante Putxinellis</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>restaurante-putxinellis-2</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/restaurante-putxinellis-2</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Restaurante Putxinellis 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>restaurante-verde-luna</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/restaurante-verde-luna</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Restaurante Verde Luna</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>restaurante-verde-luna-2</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/restaurante-verde-luna-2</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Restaurante Verde Luna 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>restaurante-verde-luna-3</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>https://xaviergp2003-gif.github.io/restaurante-verde-luna-3</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Restaurante Verde Luna 3</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" display="https://xaviergp2003-gif.github.io/allombra-del-castello" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" display="https://xaviergp2003-gif.github.io/allombra-del-castello-2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" display="https://xaviergp2003-gif.github.io/allombra-del-castello-3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" display="https://xaviergp2003-gif.github.io/arte-corte" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" display="https://xaviergp2003-gif.github.io/arte-corte-2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" display="https://xaviergp2003-gif.github.io/barberia-lat-n-art-peluqueria-unisex-barber-shop" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" display="https://xaviergp2003-gif.github.io/barberia-lat-n-art-peluqueria-unisex-barber-shop-2" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" display="https://xaviergp2003-gif.github.io/belleza-de-lidiia" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" display="https://xaviergp2003-gif.github.io/belleza-de-lidiia-2" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" display="https://xaviergp2003-gif.github.io/brume-brunch-poblenou-barcelona" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" display="https://xaviergp2003-gif.github.io/brume-brunch-poblenou-barcelona-2" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" display="https://xaviergp2003-gif.github.io/caps-p" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" display="https://xaviergp2003-gif.github.io/caps-p-2" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" display="https://xaviergp2003-gif.github.io/casa-escarr-gav" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" display="https://xaviergp2003-gif.github.io/casa-escarr-gav-2" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" display="https://xaviergp2003-gif.github.io/da-dina-restaurante-y-pizzeria" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" display="https://xaviergp2003-gif.github.io/el-cuisto" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" display="https://xaviergp2003-gif.github.io/el-cuisto-2" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" display="https://xaviergp2003-gif.github.io/el-cullerot-de-sants" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" display="https://xaviergp2003-gif.github.io/el-cullerot-de-sants-2" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" display="https://xaviergp2003-gif.github.io/global-belleza-peluqueria-sitges" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" display="https://xaviergp2003-gif.github.io/global-belleza-peluqueria-sitges-2" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" display="https://xaviergp2003-gif.github.io/gracia-d-ner-kebab" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" display="https://xaviergp2003-gif.github.io/gracia-d-ner-kebab-2" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" display="https://xaviergp2003-gif.github.io/hair-studio-arte-de-belleza-by-emil-hintz" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" display="https://xaviergp2003-gif.github.io/hair-studio-arte-de-belleza-by-emil-hintz-2" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" display="https://xaviergp2003-gif.github.io/il-mago-restaurante-pizzeria-italiana" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" display="https://xaviergp2003-gif.github.io/il-mago-restaurante-pizzeria-italiana-2" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" display="https://xaviergp2003-gif.github.io/il-nuovo-italiano-3" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" display="https://xaviergp2003-gif.github.io/la-piazzetta-granvia" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" display="https://xaviergp2003-gif.github.io/la-piazzetta-granvia-2" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" display="https://xaviergp2003-gif.github.io/la-pizza-loca" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" display="https://xaviergp2003-gif.github.io/la-pizza-loca-2" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" display="https://xaviergp2003-gif.github.io/nou-i-cl-ssic" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" display="https://xaviergp2003-gif.github.io/nou-i-cl-ssic-2" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" display="https://xaviergp2003-gif.github.io/ovvio-pizzer-a" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" display="https://xaviergp2003-gif.github.io/ovvio-pizzer-a-2" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" display="https://xaviergp2003-gif.github.io/panepizza" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" display="https://xaviergp2003-gif.github.io/panepizza-2" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" display="https://xaviergp2003-gif.github.io/peluqueria-bm-unisex" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" display="https://xaviergp2003-gif.github.io/peluqueria-bm-unisex-2" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" display="https://xaviergp2003-gif.github.io/peluqueria-cris-sitges-sl" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" display="https://xaviergp2003-gif.github.io/peluqueria-cris-sitges-sl-2" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" display="https://xaviergp2003-gif.github.io/peppe-e-pizza-gracia-pizzeria-barcelona" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" display="https://xaviergp2003-gif.github.io/peppe-e-pizza-gracia-pizzeria-barcelona-2" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" display="https://xaviergp2003-gif.github.io/peppe-e-pizza-gracia-pizzeria-barcelona-3" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" display="https://xaviergp2003-gif.github.io/pizza-rico-hospitalet" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" display="https://xaviergp2003-gif.github.io/pizza-rico-hospitalet-2" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" display="https://xaviergp2003-gif.github.io/pizzeria-etna" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" display="https://xaviergp2003-gif.github.io/pizzeria-etna-2" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" display="https://xaviergp2003-gif.github.io/pizzeria-italiana-pappa-e-pizza-cocina-italiana" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" display="https://xaviergp2003-gif.github.io/pizzeria-italiana-pappa-e-pizza-cocina-italiana-2" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B54" display="https://xaviergp2003-gif.github.io/pizzeria-naranjito" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" display="https://xaviergp2003-gif.github.io/pizzeria-naranjito-2" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" display="https://xaviergp2003-gif.github.io/pizzeria-romana" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B57" display="https://xaviergp2003-gif.github.io/pizzeria-romana-2" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B58" display="https://xaviergp2003-gif.github.io/pizzeria-san-marino" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B59" display="https://xaviergp2003-gif.github.io/pizzeria-san-marino-2" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" display="https://xaviergp2003-gif.github.io/pizzer-a-artesanal-divina-stefy" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" display="https://xaviergp2003-gif.github.io/pizzer-a-artesanal-divina-stefy-2" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" display="https://xaviergp2003-gif.github.io/pizzer-a-la-svolta" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B63" display="https://xaviergp2003-gif.github.io/pizzer-a-la-svolta-2" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" display="https://xaviergp2003-gif.github.io/pizzicato-go-badalona" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B65" display="https://xaviergp2003-gif.github.io/pizzicato-go-badalona-2" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B66" display="https://xaviergp2003-gif.github.io/prestige-peluqueros-sitges" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B67" display="https://xaviergp2003-gif.github.io/prestige-peluqueros-sitges-2" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" display="https://xaviergp2003-gif.github.io/prestige-peluqueros-sitges-3" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B69" display="https://xaviergp2003-gif.github.io/prestige-peluqueros-sitges-4" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B70" display="https://xaviergp2003-gif.github.io/restaurante-pizzeria-ed-n" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B71" display="https://xaviergp2003-gif.github.io/restaurante-pizzeria-ed-n-2" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B72" display="https://xaviergp2003-gif.github.io/restaurante-pizzeria-isabella" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" display="https://xaviergp2003-gif.github.io/restaurante-pizzeria-isabella-1" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" display="https://xaviergp2003-gif.github.io/restaurante-pizzeria-isabella-2" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B75" display="https://xaviergp2003-gif.github.io/restaurante-pizzeria-isabella-3" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" display="https://xaviergp2003-gif.github.io/restaurante-pizzeria-isabella-4" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" display="https://xaviergp2003-gif.github.io/restaurante-pizzeria-isabella-5" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B78" display="https://xaviergp2003-gif.github.io/restaurante-pizzeria-isabella-6" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B79" display="https://xaviergp2003-gif.github.io/restaurante-putxinellis" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B80" display="https://xaviergp2003-gif.github.io/restaurante-putxinellis-2" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B81" display="https://xaviergp2003-gif.github.io/restaurante-verde-luna" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B82" display="https://xaviergp2003-gif.github.io/restaurante-verde-luna-2" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B83" display="https://xaviergp2003-gif.github.io/restaurante-verde-luna-3" r:id="rId82"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>